--- a/artfynd/A 1691-2026 artfynd.xlsx
+++ b/artfynd/A 1691-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>1317485</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439969.0311700185</v>
+        <v>439969</v>
       </c>
       <c r="R2" t="n">
-        <v>6702151.427526825</v>
+        <v>6702151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1761116</v>
+        <v>1761115</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439971.8477970801</v>
+        <v>439973</v>
       </c>
       <c r="R3" t="n">
-        <v>6702351.243982081</v>
+        <v>6702330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +858,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1761115</v>
+        <v>1761116</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439972.9787404811</v>
+        <v>439972</v>
       </c>
       <c r="R4" t="n">
-        <v>6702330.005728269</v>
+        <v>6702351</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,19 +964,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1691-2026 artfynd.xlsx
+++ b/artfynd/A 1691-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1317485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1761115</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1761116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>